--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126463759</v>
+        <v>126463890</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>91241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575180</v>
+        <v>575267</v>
       </c>
       <c r="R7" t="n">
-        <v>7303253</v>
+        <v>7303578</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126463890</v>
+        <v>126463759</v>
       </c>
       <c r="B8" t="n">
-        <v>91241</v>
+        <v>75075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575267</v>
+        <v>575180</v>
       </c>
       <c r="R8" t="n">
-        <v>7303578</v>
+        <v>7303253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126463861</v>
+        <v>126463907</v>
       </c>
       <c r="B12" t="n">
         <v>91263</v>
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575277</v>
+        <v>575473</v>
       </c>
       <c r="R12" t="n">
-        <v>7303478</v>
+        <v>7303652</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126463907</v>
+        <v>126463861</v>
       </c>
       <c r="B13" t="n">
         <v>91263</v>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575473</v>
+        <v>575277</v>
       </c>
       <c r="R13" t="n">
-        <v>7303652</v>
+        <v>7303478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126463878</v>
+        <v>126463819</v>
       </c>
       <c r="B14" t="n">
-        <v>91263</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575298</v>
+        <v>575159</v>
       </c>
       <c r="R14" t="n">
-        <v>7303550</v>
+        <v>7303370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,6 +2022,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,32 +2165,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126463819</v>
+        <v>126463878</v>
       </c>
       <c r="B16" t="n">
-        <v>92535</v>
+        <v>91263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575159</v>
+        <v>575298</v>
       </c>
       <c r="R16" t="n">
-        <v>7303370</v>
+        <v>7303550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -2483,38 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126463926</v>
+        <v>126463831</v>
       </c>
       <c r="B19" t="n">
-        <v>98265</v>
+        <v>80084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2522,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575425</v>
+        <v>575158</v>
       </c>
       <c r="R19" t="n">
-        <v>7303667</v>
+        <v>7303499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,37 +2589,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126463831</v>
+        <v>126463914</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>105381</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575158</v>
+        <v>575425</v>
       </c>
       <c r="R20" t="n">
-        <v>7303499</v>
+        <v>7303667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126463914</v>
+        <v>126463926</v>
       </c>
       <c r="B21" t="n">
-        <v>105381</v>
+        <v>98265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126463819</v>
+        <v>126463894</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>91241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575159</v>
+        <v>575259</v>
       </c>
       <c r="R14" t="n">
-        <v>7303370</v>
+        <v>7303609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,11 +2022,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,32 +2054,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126463894</v>
+        <v>126463819</v>
       </c>
       <c r="B15" t="n">
-        <v>91241</v>
+        <v>92535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575259</v>
+        <v>575159</v>
       </c>
       <c r="R15" t="n">
-        <v>7303609</v>
+        <v>7303370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,6 +2128,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,37 +2483,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126463831</v>
+        <v>126463914</v>
       </c>
       <c r="B19" t="n">
-        <v>80084</v>
+        <v>105381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575158</v>
+        <v>575425</v>
       </c>
       <c r="R19" t="n">
-        <v>7303499</v>
+        <v>7303667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126463914</v>
+        <v>126463926</v>
       </c>
       <c r="B20" t="n">
-        <v>105381</v>
+        <v>98265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,38 +2697,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126463926</v>
+        <v>126463831</v>
       </c>
       <c r="B21" t="n">
-        <v>98265</v>
+        <v>80084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575158</v>
       </c>
       <c r="R21" t="n">
-        <v>7303667</v>
+        <v>7303499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -781,37 +781,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126463897</v>
+        <v>126463865</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>57761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575259</v>
+        <v>575278</v>
       </c>
       <c r="R3" t="n">
-        <v>7303609</v>
+        <v>7303478</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +864,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,38 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126463865</v>
+        <v>126463897</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575278</v>
+        <v>575259</v>
       </c>
       <c r="R4" t="n">
-        <v>7303478</v>
+        <v>7303609</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +969,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2483,38 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126463914</v>
+        <v>126463831</v>
       </c>
       <c r="B19" t="n">
-        <v>105381</v>
+        <v>80084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2522,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575425</v>
+        <v>575158</v>
       </c>
       <c r="R19" t="n">
-        <v>7303667</v>
+        <v>7303499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126463926</v>
+        <v>126463914</v>
       </c>
       <c r="B20" t="n">
-        <v>98265</v>
+        <v>105381</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,21 +2600,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2697,37 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126463831</v>
+        <v>126463926</v>
       </c>
       <c r="B21" t="n">
-        <v>80084</v>
+        <v>98265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575158</v>
+        <v>575425</v>
       </c>
       <c r="R21" t="n">
-        <v>7303499</v>
+        <v>7303667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -781,38 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126463865</v>
+        <v>126463897</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>91263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575278</v>
+        <v>575259</v>
       </c>
       <c r="R3" t="n">
-        <v>7303478</v>
+        <v>7303609</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,37 +887,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126463897</v>
+        <v>126463865</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>57761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575259</v>
+        <v>575278</v>
       </c>
       <c r="R4" t="n">
-        <v>7303609</v>
+        <v>7303478</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +970,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2483,37 +2483,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126463831</v>
+        <v>126463914</v>
       </c>
       <c r="B19" t="n">
-        <v>80084</v>
+        <v>105381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575158</v>
+        <v>575425</v>
       </c>
       <c r="R19" t="n">
-        <v>7303499</v>
+        <v>7303667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126463914</v>
+        <v>126463926</v>
       </c>
       <c r="B20" t="n">
-        <v>105381</v>
+        <v>98265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,38 +2697,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126463926</v>
+        <v>126463831</v>
       </c>
       <c r="B21" t="n">
-        <v>98265</v>
+        <v>80084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575425</v>
+        <v>575158</v>
       </c>
       <c r="R21" t="n">
-        <v>7303667</v>
+        <v>7303499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126463767</v>
+        <v>126463846</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575196</v>
+        <v>575129</v>
       </c>
       <c r="R2" t="n">
-        <v>7303267</v>
+        <v>7303534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126463897</v>
+        <v>126463890</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575259</v>
+        <v>575267</v>
       </c>
       <c r="R3" t="n">
-        <v>7303609</v>
+        <v>7303578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,38 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126463865</v>
+        <v>126463894</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575278</v>
+        <v>575259</v>
       </c>
       <c r="R4" t="n">
-        <v>7303478</v>
+        <v>7303609</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +969,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126463751</v>
+        <v>126463842</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575187</v>
+        <v>575129</v>
       </c>
       <c r="R5" t="n">
-        <v>7303245</v>
+        <v>7303534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126463842</v>
+        <v>126463767</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575129</v>
+        <v>575196</v>
       </c>
       <c r="R6" t="n">
-        <v>7303534</v>
+        <v>7303267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126463759</v>
+        <v>126463831</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575180</v>
+        <v>575158</v>
       </c>
       <c r="R7" t="n">
-        <v>7303253</v>
+        <v>7303499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126463890</v>
+        <v>126463819</v>
       </c>
       <c r="B8" t="n">
-        <v>91241</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575267</v>
+        <v>575159</v>
       </c>
       <c r="R8" t="n">
-        <v>7303578</v>
+        <v>7303370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,38 +1422,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126463917</v>
+        <v>126463751</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575425</v>
+        <v>575187</v>
       </c>
       <c r="R9" t="n">
-        <v>7303667</v>
+        <v>7303245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,32 +1528,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126463771</v>
+        <v>126463759</v>
       </c>
       <c r="B10" t="n">
-        <v>79987</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575196</v>
+        <v>575180</v>
       </c>
       <c r="R10" t="n">
-        <v>7303267</v>
+        <v>7303253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,32 +1634,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126463846</v>
+        <v>126463771</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575129</v>
+        <v>575196</v>
       </c>
       <c r="R11" t="n">
-        <v>7303534</v>
+        <v>7303267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,32 +1740,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126463907</v>
+        <v>126463834</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1774,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575473</v>
+        <v>575158</v>
       </c>
       <c r="R12" t="n">
-        <v>7303652</v>
+        <v>7303499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126463861</v>
+        <v>126463865</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>58057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,26 +1857,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1880,13 +1885,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575277</v>
+        <v>575278</v>
       </c>
       <c r="R13" t="n">
         <v>7303478</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1948,37 +1952,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126463894</v>
+        <v>126463926</v>
       </c>
       <c r="B14" t="n">
-        <v>91241</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575259</v>
+        <v>575425</v>
       </c>
       <c r="R14" t="n">
-        <v>7303609</v>
+        <v>7303667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126463819</v>
+        <v>126463914</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>106229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,26 +2070,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2092,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575159</v>
+        <v>575425</v>
       </c>
       <c r="R15" t="n">
-        <v>7303370</v>
+        <v>7303667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,11 +2134,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjolårskroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,37 +2166,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126463878</v>
+        <v>126463917</v>
       </c>
       <c r="B16" t="n">
-        <v>91263</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575298</v>
+        <v>575425</v>
       </c>
       <c r="R16" t="n">
-        <v>7303550</v>
+        <v>7303667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,538 +2270,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>126463808</v>
-      </c>
-      <c r="B17" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gäddträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>575170</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7303374</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>126463834</v>
-      </c>
-      <c r="B18" t="n">
-        <v>80112</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Gäddträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>575158</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7303499</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>126463831</v>
-      </c>
-      <c r="B19" t="n">
-        <v>80084</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Gäddträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>575158</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7303499</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>126463914</v>
-      </c>
-      <c r="B20" t="n">
-        <v>105381</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Gäddträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>575425</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7303667</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>126463926</v>
-      </c>
-      <c r="B21" t="n">
-        <v>98265</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Gäddträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>575425</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7303667</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57566-2024 artfynd.xlsx
+++ b/artfynd/A 57566-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463842</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463831</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463819</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463751</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463771</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463834</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1949,6 +2009,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463865</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2056,6 +2121,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463926</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2163,6 +2233,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463914</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,8 +2345,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126463917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>